--- a/Common/Style/Resource/Template/Import_Interessent.xlsx
+++ b/Common/Style/Resource/Template/Import_Interessent.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\siddy\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5546404-D795-4CE8-A9BA-828202D28783}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36DBC36F-C539-463F-93A4-60D102ADDAC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Interessent" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Interessent!$A$2:$AX$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">Interessent!$A$2:$AY$2</definedName>
   </definedNames>
   <calcPr calcId="145621"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="79">
   <si>
     <t>Nr</t>
   </si>
@@ -259,24 +259,25 @@
   </si>
   <si>
     <t>01.01.2020</t>
+  </si>
+  <si>
+    <t>Optional</t>
+  </si>
+  <si>
+    <t>ImportId</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="MS Sans Serif"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -342,7 +343,7 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
@@ -353,16 +354,16 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="49" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="14" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -693,7 +694,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:AX2"/>
+  <dimension ref="A1:AY2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.140625" style="1" bestFit="1" customWidth="1"/>
@@ -724,14 +725,14 @@
     <col min="26" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="12.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="18.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="32" width="11.5703125" style="1"/>
-    <col min="33" max="33" width="20.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="43" width="11.5703125" style="1"/>
-    <col min="44" max="44" width="20.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="45" max="16384" width="11.5703125" style="1"/>
+    <col min="29" max="33" width="11.5703125" style="1"/>
+    <col min="34" max="34" width="20.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="44" width="11.5703125" style="1"/>
+    <col min="45" max="45" width="20.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="46" max="16384" width="11.5703125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:50" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:51" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5"/>
       <c r="B1" s="6" t="s">
         <v>14</v>
@@ -813,73 +814,76 @@
         <v>42</v>
       </c>
       <c r="AC1" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="AD1" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="AD1" s="6" t="s">
+      <c r="AE1" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="AE1" s="6" t="s">
+      <c r="AF1" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="AF1" s="6" t="s">
+      <c r="AG1" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="AG1" s="6" t="s">
+      <c r="AH1" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="AH1" s="6" t="s">
+      <c r="AI1" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="AI1" s="6" t="s">
+      <c r="AJ1" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="AJ1" s="6" t="s">
+      <c r="AK1" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="AK1" s="6" t="s">
+      <c r="AL1" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="AL1" s="6">
+      <c r="AM1" s="6">
         <v>7</v>
       </c>
-      <c r="AM1" s="6" t="s">
+      <c r="AN1" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="AN1" s="6" t="s">
+      <c r="AO1" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="AO1" s="6" t="s">
+      <c r="AP1" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="AP1" s="6" t="s">
+      <c r="AQ1" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="AQ1" s="6" t="s">
+      <c r="AR1" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="AR1" s="6" t="s">
+      <c r="AS1" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="AS1" s="6" t="s">
+      <c r="AT1" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="AT1" s="6" t="s">
+      <c r="AU1" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="AU1" s="6" t="s">
+      <c r="AV1" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="AV1" s="6" t="s">
+      <c r="AW1" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="AW1" s="6">
+      <c r="AX1" s="6">
         <v>7</v>
       </c>
-      <c r="AX1" s="6" t="s">
+      <c r="AY1" s="6" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="2" spans="1:50" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:51" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
         <v>0</v>
       </c>
@@ -964,76 +968,79 @@
       <c r="AB2" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="AC2" s="10" t="s">
+      <c r="AC2" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD2" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="AD2" s="10" t="s">
+      <c r="AE2" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="AE2" s="10" t="s">
+      <c r="AF2" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="AF2" s="10" t="s">
+      <c r="AG2" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="AG2" s="10" t="s">
+      <c r="AH2" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="AH2" s="10" t="s">
+      <c r="AI2" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="AI2" s="10" t="s">
+      <c r="AJ2" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="AJ2" s="10" t="s">
+      <c r="AK2" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="AK2" s="10" t="s">
+      <c r="AL2" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="AL2" s="10" t="s">
+      <c r="AM2" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="AM2" s="10" t="s">
+      <c r="AN2" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="AN2" s="11" t="s">
+      <c r="AO2" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="AO2" s="11" t="s">
+      <c r="AP2" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="AP2" s="11" t="s">
+      <c r="AQ2" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="AQ2" s="11" t="s">
+      <c r="AR2" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="AR2" s="11" t="s">
+      <c r="AS2" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="AS2" s="11" t="s">
+      <c r="AT2" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="AT2" s="11" t="s">
+      <c r="AU2" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="AU2" s="11" t="s">
+      <c r="AV2" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="AV2" s="11" t="s">
+      <c r="AW2" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="AW2" s="11" t="s">
+      <c r="AX2" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="AX2" s="11" t="s">
+      <c r="AY2" s="11" t="s">
         <v>68</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="0MRvk69Fc+TPRySQgWXv3uWmn8ot1EaVGOL4iW+oW0z/k9koGk8lFCCsmvj4+JRpmb7stcshTg/RX9w1lx1gjA==" saltValue="+AUFqvzqG9HbYCcG4gHwLw==" spinCount="100000" sheet="1" objects="1" scenarios="1" formatColumns="0" formatRows="0" insertRows="0" deleteRows="0" sort="0" autoFilter="0"/>
-  <autoFilter ref="A2:AX2" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="jsxn5tBF+IKvDUe61u08wQ3QpqyeK8e4Zwny2N02xpyYJUdWEjxX4JwJe4bMxEIzMHXhEzPErby74Q/kB9p77g==" saltValue="jIUBXSkzfTkFdksBsH9Vag==" spinCount="100000" sheet="1" formatColumns="0" formatRows="0" insertRows="0" deleteRows="0" sort="0" autoFilter="0"/>
+  <autoFilter ref="A2:AY2" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="4294967293" r:id="rId1"/>
 </worksheet>
